--- a/GenericBookingTemplate.xlsx
+++ b/GenericBookingTemplate.xlsx
@@ -1165,24 +1165,20 @@
       </c>
       <c r="AK1" s="7" t="inlineStr">
         <is>
-          <t>INFANTSEAT</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="AL1" s="7" t="inlineStr">
         <is>
-          <t>BOOSTERSEAT</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="AM1" s="7" t="inlineStr">
         <is>
-          <t>CS</t>
-        </is>
-      </c>
-      <c r="AN1" s="7" t="inlineStr">
-        <is>
           <t>YD</t>
         </is>
       </c>
+      <c r="AN1" s="7" t="n"/>
       <c r="AO1" s="7" t="n"/>
       <c r="AP1" s="7" t="n"/>
       <c r="AQ1" s="7" t="n"/>
